--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="150">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -284,6 +284,9 @@
   <si>
     <t xml:space="preserve">Identifier
 </t>
+  </si>
+  <si>
+    <t>UUID SOP instance</t>
   </si>
   <si>
     <t>Identifiant de l’entrée</t>
@@ -448,13 +451,7 @@
     <t>fr-lm-entry.header.language</t>
   </si>
   <si>
-    <t>fr-lm-sop-instance.uuidSOPInstance</t>
-  </si>
-  <si>
-    <t>UUID SOP instance</t>
-  </si>
-  <si>
-    <t>fr-lm-sop-instance.classeSOP</t>
+    <t>fr-lm-sop-instance.sopClass</t>
   </si>
   <si>
     <t>Classe SOP</t>
@@ -463,14 +460,23 @@
     <t>JDV-SOPClass_CISIS (1.2.250.1.213.1.1.5.689)</t>
   </si>
   <si>
-    <t>fr-lm-sop-instance.nombreCadresReferences</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-sop-instance.instanceNumber</t>
   </si>
   <si>
     <t xml:space="preserve">integer
 </t>
   </si>
   <si>
-    <t>Nombres de cadres référencés</t>
+    <t>Numéro de l'instance dans la série</t>
+  </si>
+  <si>
+    <t>fr-lm-sop-instance.numberOfFrames</t>
+  </si>
+  <si>
+    <t>Nombre de cadres composant l'instance</t>
   </si>
 </sst>
 </file>
@@ -800,7 +806,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="37.05859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.76953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1235,7 +1241,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>75</v>
@@ -1256,7 +1262,7 @@
         <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1307,7 +1313,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -1324,10 +1330,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1353,10 +1359,10 @@
         <v>80</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1407,7 +1413,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1424,10 +1430,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1450,13 +1456,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1507,7 +1513,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1524,10 +1530,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1550,13 +1556,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1607,7 +1613,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1624,10 +1630,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1650,13 +1656,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1707,7 +1713,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1724,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1750,13 +1756,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1807,7 +1813,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1824,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1853,10 +1859,10 @@
         <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1907,7 +1913,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1924,10 +1930,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1950,13 +1956,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2007,7 +2013,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2024,10 +2030,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2050,13 +2056,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2107,7 +2113,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2124,10 +2130,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2150,13 +2156,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2207,7 +2213,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2224,10 +2230,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2250,13 +2256,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2307,7 +2313,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2324,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2350,13 +2356,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2407,7 +2413,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2424,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2450,13 +2456,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2507,7 +2513,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2524,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2550,13 +2556,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2607,7 +2613,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2624,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2650,13 +2656,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2707,7 +2713,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2724,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2738,7 +2744,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2750,13 +2756,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2786,10 +2792,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2807,13 +2813,13 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
@@ -2824,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2835,7 +2841,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2850,13 +2856,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2886,7 +2892,7 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>73</v>
@@ -2907,10 +2913,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -2924,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2953,10 +2959,10 @@
         <v>146</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3007,7 +3013,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
